--- a/hexo/hexo/source/_posts/video-scripts/口播稿/data/作品列表.xlsx
+++ b/hexo/hexo/source/_posts/video-scripts/口播稿/data/作品列表.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="316">
   <si>
     <t>作品名称</t>
   </si>
@@ -66,552 +66,696 @@
     <t>粉丝增量</t>
   </si>
   <si>
+    <t>ChatGPT正在变成超级App，但真正危险的不是功能多 #我在抖音聊科技 #用ai干我这行 #chatgpt #codex #agent</t>
+  </si>
+  <si>
+    <t>2026-06-12 19:26:14</t>
+  </si>
+  <si>
+    <t>1-3min视频</t>
+  </si>
+  <si>
+    <t>公开</t>
+  </si>
+  <si>
+    <t>588</t>
+  </si>
+  <si>
+    <t>0.027444</t>
+  </si>
+  <si>
+    <t>0.354992</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>0.400951</t>
+  </si>
+  <si>
+    <t>8.664025</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>瑞幸点单都被AI接管了，你还在手动加班？ #我在抖音聊科技 #瑞幸 #skill #agent</t>
+  </si>
+  <si>
+    <t>2026-06-11 08:00:00</t>
+  </si>
+  <si>
+    <t>306</t>
+  </si>
+  <si>
+    <t>0.015924</t>
+  </si>
+  <si>
+    <t>0.191489</t>
+  </si>
+  <si>
+    <t>0.571429</t>
+  </si>
+  <si>
+    <t>6.593373</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>AI能写代码能画画，但考不上大学 #ai专业 #我在抖音聊科技 #高考</t>
+  </si>
+  <si>
+    <t>2026-06-10 08:21:00</t>
+  </si>
+  <si>
+    <t>389</t>
+  </si>
+  <si>
+    <t>0.038781</t>
+  </si>
+  <si>
+    <t>0.356962</t>
+  </si>
+  <si>
+    <t>0.437975</t>
+  </si>
+  <si>
+    <t>11.238443</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>你身边还没人聊Codex？那你运气来了 #ai学习工具 #我在抖音聊科技 #智能办公工具 #职场技能升级指南 #ai工具测评</t>
+  </si>
+  <si>
+    <t>2026-06-09 08:46:00</t>
+  </si>
+  <si>
+    <t>3502</t>
+  </si>
+  <si>
+    <t>0.025953</t>
+  </si>
+  <si>
+    <t>0.366319</t>
+  </si>
+  <si>
+    <t>0.398810</t>
+  </si>
+  <si>
+    <t>11.544693</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>openai最新报告，打工人必须用上AI #我在抖音聊科技 #一本正经分享 #ai</t>
+  </si>
+  <si>
+    <t>2026-06-08 08:10:00</t>
+  </si>
+  <si>
+    <t>1min-视频</t>
+  </si>
+  <si>
+    <t>1599</t>
+  </si>
+  <si>
+    <t>0.072575</t>
+  </si>
+  <si>
+    <t>0.538259</t>
+  </si>
+  <si>
+    <t>0.260554</t>
+  </si>
+  <si>
+    <t>13.356043</t>
+  </si>
+  <si>
+    <t>拉勾网申请破产，AI招聘来了 #我在抖音聊科技 #拉勾网 #破产 #AI #校招和社招</t>
+  </si>
+  <si>
+    <t>2026-06-07 08:02:00</t>
+  </si>
+  <si>
+    <t>3254</t>
+  </si>
+  <si>
+    <t>0.061018</t>
+  </si>
+  <si>
+    <t>0.504968</t>
+  </si>
+  <si>
+    <t>0.277615</t>
+  </si>
+  <si>
+    <t>13.149541</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>AI，我只用国产 #我在抖音聊科技 #国产ai #ai工具避坑指南 #ai工具测评 #ai工具使用心得</t>
   </si>
   <si>
     <t>2026-06-05 15:29:00</t>
   </si>
   <si>
-    <t>1-3min视频</t>
-  </si>
-  <si>
-    <t>公开</t>
-  </si>
-  <si>
-    <t>2307</t>
-  </si>
-  <si>
-    <t>0.092164</t>
-  </si>
-  <si>
-    <t>0.484663</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>0.231084</t>
-  </si>
-  <si>
-    <t>24.385621</t>
+    <t>2413</t>
+  </si>
+  <si>
+    <t>0.089695</t>
+  </si>
+  <si>
+    <t>0.472233</t>
+  </si>
+  <si>
+    <t>0.243968</t>
+  </si>
+  <si>
+    <t>23.422180</t>
   </si>
   <si>
     <t>36</t>
   </si>
   <si>
-    <t>1</t>
+    <t>24</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>会用AI的女人，到底有多好 #我在抖音聊科技 #知识分享内容太过真实 #个人经验分析 #说真话的博主 #ai个人观点</t>
+  </si>
+  <si>
+    <t>2026-06-04 19:31:31</t>
+  </si>
+  <si>
+    <t>671</t>
+  </si>
+  <si>
+    <t>0.025992</t>
+  </si>
+  <si>
+    <t>0.328165</t>
+  </si>
+  <si>
+    <t>0.319121</t>
+  </si>
+  <si>
+    <t>6.950904</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>我求你别去碰Claude Code #我在抖音聊科技 #claude #ai</t>
+  </si>
+  <si>
+    <t>2026-06-03 21:38:55</t>
+  </si>
+  <si>
+    <t>4170</t>
+  </si>
+  <si>
+    <t>0.028864</t>
+  </si>
+  <si>
+    <t>0.470010</t>
+  </si>
+  <si>
+    <t>0.319540</t>
+  </si>
+  <si>
+    <t>13.424008</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>姐妹你要把握住：会用AI的男人 #说真话的博主 #认知提升 #我在抖音聊科技 #codex #恋爱</t>
+  </si>
+  <si>
+    <t>2026-05-24 11:07:00</t>
+  </si>
+  <si>
+    <t>4073</t>
+  </si>
+  <si>
+    <t>0.033486</t>
+  </si>
+  <si>
+    <t>0.403937</t>
+  </si>
+  <si>
+    <t>0.310236</t>
+  </si>
+  <si>
+    <t>9.142673</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>腾讯文档大裁员？我查到了真相 #说真话的博主 #我在抖音聊科技 #裁员 #腾讯文档</t>
+  </si>
+  <si>
+    <t>2026-05-23 18:11:48</t>
+  </si>
+  <si>
+    <t>5407</t>
+  </si>
+  <si>
+    <t>0.123351</t>
+  </si>
+  <si>
+    <t>0.459045</t>
+  </si>
+  <si>
+    <t>0.286016</t>
+  </si>
+  <si>
+    <t>12.928506</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>淘汰你的不是AI，是被AI武装过的新人 #ai #大模型 #亚马逊 #我在抖音聊科技 #ai对话日常</t>
+  </si>
+  <si>
+    <t>2026-05-20 08:52:28</t>
+  </si>
+  <si>
+    <t>631</t>
+  </si>
+  <si>
+    <t>0.019878</t>
+  </si>
+  <si>
+    <t>0.279370</t>
+  </si>
+  <si>
+    <t>0.478510</t>
+  </si>
+  <si>
+    <t>10.987198</t>
+  </si>
+  <si>
+    <t>OpenAI亏损超100亿，免费要成为历史？ #我在抖音聊科技 #科技下一站 #与ai同行 #我的ai同事</t>
+  </si>
+  <si>
+    <t>2026-05-14 17:47:34</t>
+  </si>
+  <si>
+    <t>3975</t>
+  </si>
+  <si>
+    <t>0.027370</t>
+  </si>
+  <si>
+    <t>0.460627</t>
+  </si>
+  <si>
+    <t>0.298311</t>
+  </si>
+  <si>
+    <t>17.944834</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>20</t>
   </si>
   <si>
     <t>21</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>会用AI的女人，到底有多好 #我在抖音聊科技 #知识分享内容太过真实 #个人经验分析 #说真话的博主 #ai个人观点</t>
-  </si>
-  <si>
-    <t>2026-06-04 19:31:31</t>
-  </si>
-  <si>
-    <t>1min-视频</t>
-  </si>
-  <si>
-    <t>623</t>
-  </si>
-  <si>
-    <t>0.028744</t>
-  </si>
-  <si>
-    <t>0.350427</t>
-  </si>
-  <si>
-    <t>0.290598</t>
-  </si>
-  <si>
-    <t>7.371795</t>
+    <t>教你用AI的人，可能自己都不用。#我在抖音聊科技 #科技下一站 #与ai同行</t>
+  </si>
+  <si>
+    <t>2026-05-13 21:35:01</t>
+  </si>
+  <si>
+    <t>525</t>
+  </si>
+  <si>
+    <t>0.042553</t>
+  </si>
+  <si>
+    <t>0.352190</t>
+  </si>
+  <si>
+    <t>0.370438</t>
+  </si>
+  <si>
+    <t>14.070144</t>
   </si>
   <si>
     <t>11</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>我求你别去碰Claude Code #我在抖音聊科技 #claude #ai</t>
-  </si>
-  <si>
-    <t>2026-06-03 21:38:55</t>
-  </si>
-  <si>
-    <t>3396</t>
-  </si>
-  <si>
-    <t>0.029893</t>
-  </si>
-  <si>
-    <t>0.489992</t>
-  </si>
-  <si>
-    <t>0.296075</t>
-  </si>
-  <si>
-    <t>13.649610</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>15</t>
+    <t>GPT-5.5突然被禁了？OpenAI内部到底发生了什么#我在抖音聊科技 #科技下一站 #假期宅家日记 #ai</t>
+  </si>
+  <si>
+    <t>2026-05-06 20:53:28</t>
+  </si>
+  <si>
+    <t>2636</t>
+  </si>
+  <si>
+    <t>0.046929</t>
+  </si>
+  <si>
+    <t>0.527543</t>
+  </si>
+  <si>
+    <t>0.285569</t>
+  </si>
+  <si>
+    <t>22.179350</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>大厂AI开始收费，普通人怎么办？ #科技下一站 #与ai同行 #假期宅家日记 #腾讯 #豆包</t>
+  </si>
+  <si>
+    <t>2026-05-05 16:33:34</t>
+  </si>
+  <si>
+    <t>10468</t>
+  </si>
+  <si>
+    <t>0.019194</t>
+  </si>
+  <si>
+    <t>0.261682</t>
+  </si>
+  <si>
+    <t>0.522932</t>
+  </si>
+  <si>
+    <t>14.037229</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>豆包宣布要收费了，最高每月500，免费AI还能撑多久？ #科技下一站 #与ai同行 #豆包</t>
+  </si>
+  <si>
+    <t>2026-05-04 20:43:25</t>
+  </si>
+  <si>
+    <t>20374</t>
+  </si>
+  <si>
+    <t>0.010046</t>
+  </si>
+  <si>
+    <t>0.397471</t>
+  </si>
+  <si>
+    <t>0.416726</t>
+  </si>
+  <si>
+    <t>12.628034</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>AI这么强，为什么大部分公司用不起来？#假期宅家日记 #科技下一站 #我在抖音聊科技 #一本正经说实在话 #ai</t>
+  </si>
+  <si>
+    <t>2026-05-04 11:20:35</t>
+  </si>
+  <si>
+    <t>607</t>
+  </si>
+  <si>
+    <t>0.021452</t>
+  </si>
+  <si>
+    <t>0.400616</t>
+  </si>
+  <si>
+    <t>0.328197</t>
+  </si>
+  <si>
+    <t>27.776471</t>
+  </si>
+  <si>
+    <t>为什么免费AI工具反而更值得警惕？#我在抖音聊科技 #科技下一站 #创业者说真话 #假期宅家日记 #AI</t>
+  </si>
+  <si>
+    <t>2026-05-03 08:43:00</t>
+  </si>
+  <si>
+    <t>2931</t>
+  </si>
+  <si>
+    <t>0.020052</t>
+  </si>
+  <si>
+    <t>0.500171</t>
+  </si>
+  <si>
+    <t>0.267009</t>
+  </si>
+  <si>
+    <t>20.872832</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>普通人用AI做副业 的方法 #科技下一站 #与ai同行 #假期宅家日记#副业 #自动化办公</t>
+  </si>
+  <si>
+    <t>2026-05-02 16:29:45</t>
+  </si>
+  <si>
+    <t>3-5min视频</t>
+  </si>
+  <si>
+    <t>166</t>
+  </si>
+  <si>
+    <t>0.000000</t>
+  </si>
+  <si>
+    <t>0.239234</t>
+  </si>
+  <si>
+    <t>0.105263</t>
+  </si>
+  <si>
+    <t>0.574163</t>
+  </si>
+  <si>
+    <t>8.281690</t>
+  </si>
+  <si>
+    <t>AI这么火，为什么一堆公司倒闭了？#科技下一站 #还有什么是不能ai的 #与ai同行 #大模型 #假期宅家日记</t>
+  </si>
+  <si>
+    <t>2026-04-30 22:40:21</t>
+  </si>
+  <si>
+    <t>3024</t>
+  </si>
+  <si>
+    <t>0.045107</t>
+  </si>
+  <si>
+    <t>0.546398</t>
+  </si>
+  <si>
+    <t>0.281311</t>
+  </si>
+  <si>
+    <t>29.367882</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>AI不会取代你的工作，但会用AI的人会 #AI焦虑 #自动化办公 #科技改变生活 #大模型</t>
+  </si>
+  <si>
+    <t>2026-04-30 22:00:53</t>
+  </si>
+  <si>
+    <t>182</t>
+  </si>
+  <si>
+    <t>0.026042</t>
+  </si>
+  <si>
+    <t>0.228155</t>
+  </si>
+  <si>
+    <t>0.582524</t>
+  </si>
+  <si>
+    <t>23.528846</t>
+  </si>
+  <si>
+    <t>普通人上大学，千万别学ai。 #科技下一站 #还有什么是不能ai的 #与ai同行 #高考 #专业</t>
+  </si>
+  <si>
+    <t>2026-04-29 15:08:15</t>
+  </si>
+  <si>
+    <t>577</t>
+  </si>
+  <si>
+    <t>0.022648</t>
+  </si>
+  <si>
+    <t>0.368182</t>
+  </si>
+  <si>
+    <t>0.377273</t>
+  </si>
+  <si>
+    <t>16.358974</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>家人们，我把AI的价格秘密整理出来了#说真话 #职场干货 #科技下一站 #还有什么是不能ai的 #与ai同行</t>
+  </si>
+  <si>
+    <t>2026-04-29 07:03:00</t>
+  </si>
+  <si>
+    <t>240</t>
+  </si>
+  <si>
+    <t>0.048980</t>
+  </si>
+  <si>
+    <t>0.273764</t>
+  </si>
+  <si>
+    <t>0.520913</t>
+  </si>
+  <si>
+    <t>12.380228</t>
+  </si>
+  <si>
+    <t>明明国内算力更稀缺，为什么反而更便 #科技下一站 #与ai同行 #token</t>
+  </si>
+  <si>
+    <t>2026-04-28 19:57:16</t>
+  </si>
+  <si>
+    <t>11009</t>
+  </si>
+  <si>
+    <t>0.052585</t>
+  </si>
+  <si>
+    <t>0.491795</t>
+  </si>
+  <si>
+    <t>0.293566</t>
+  </si>
+  <si>
+    <t>23.668692</t>
+  </si>
+  <si>
+    <t>164</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>165</t>
   </si>
   <si>
     <t>22</t>
   </si>
   <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>姐妹你要把握住：会用AI的男人 #说真话的博主 #认知提升 #我在抖音聊科技 #codex #恋爱</t>
-  </si>
-  <si>
-    <t>2026-05-24 11:07:00</t>
-  </si>
-  <si>
-    <t>4014</t>
-  </si>
-  <si>
-    <t>0.032878</t>
-  </si>
-  <si>
-    <t>0.404267</t>
-  </si>
-  <si>
-    <t>0.307467</t>
-  </si>
-  <si>
-    <t>9.067653</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>腾讯文档大裁员？我查到了真相 #说真话的博主 #我在抖音聊科技 #裁员 #腾讯文档</t>
-  </si>
-  <si>
-    <t>2026-05-23 18:11:48</t>
-  </si>
-  <si>
-    <t>5332</t>
-  </si>
-  <si>
-    <t>0.123856</t>
-  </si>
-  <si>
-    <t>0.460639</t>
-  </si>
-  <si>
-    <t>0.284100</t>
-  </si>
-  <si>
-    <t>12.994275</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>淘汰你的不是AI，是被AI武装过的新人 #ai #大模型 #亚马逊 #我在抖音聊科技 #ai对话日常</t>
-  </si>
-  <si>
-    <t>2026-05-20 08:52:28</t>
-  </si>
-  <si>
-    <t>531</t>
-  </si>
-  <si>
-    <t>0.021938</t>
-  </si>
-  <si>
-    <t>0.288625</t>
-  </si>
-  <si>
-    <t>0.466893</t>
-  </si>
-  <si>
-    <t>11.660473</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>OpenAI亏损超100亿，免费要成为历史？ #我在抖音聊科技 #科技下一站 #与ai同行 #我的ai同事</t>
-  </si>
-  <si>
-    <t>2026-05-14 17:47:34</t>
-  </si>
-  <si>
-    <t>3971</t>
-  </si>
-  <si>
-    <t>0.027431</t>
-  </si>
-  <si>
-    <t>0.461538</t>
-  </si>
-  <si>
-    <t>0.297582</t>
-  </si>
-  <si>
-    <t>17.977188</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>教你用AI的人，可能自己都不用。#我在抖音聊科技 #科技下一站 #与ai同行</t>
-  </si>
-  <si>
-    <t>2026-05-13 21:35:01</t>
-  </si>
-  <si>
-    <t>518</t>
-  </si>
-  <si>
-    <t>0.043564</t>
-  </si>
-  <si>
-    <t>0.357678</t>
-  </si>
-  <si>
-    <t>0.361423</t>
-  </si>
-  <si>
-    <t>14.369004</t>
-  </si>
-  <si>
-    <t>GPT-5.5突然被禁了？OpenAI内部到底发生了什么#我在抖音聊科技 #科技下一站 #假期宅家日记 #ai</t>
-  </si>
-  <si>
-    <t>2026-05-06 20:53:28</t>
-  </si>
-  <si>
-    <t>2585</t>
-  </si>
-  <si>
-    <t>0.046656</t>
-  </si>
-  <si>
-    <t>0.528399</t>
-  </si>
-  <si>
-    <t>0.285714</t>
-  </si>
-  <si>
-    <t>22.291083</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>大厂AI开始收费，普通人怎么办？ #科技下一站 #与ai同行 #假期宅家日记 #腾讯 #豆包</t>
-  </si>
-  <si>
-    <t>2026-05-05 16:33:34</t>
-  </si>
-  <si>
-    <t>9864</t>
-  </si>
-  <si>
-    <t>0.018838</t>
-  </si>
-  <si>
-    <t>0.260792</t>
-  </si>
-  <si>
-    <t>0.523841</t>
-  </si>
-  <si>
-    <t>13.365787</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>豆包宣布要收费了，最高每月500，免费AI还能撑多久？ #科技下一站 #与ai同行 #豆包</t>
-  </si>
-  <si>
-    <t>2026-05-04 20:43:25</t>
-  </si>
-  <si>
-    <t>20371</t>
-  </si>
-  <si>
-    <t>0.010048</t>
-  </si>
-  <si>
-    <t>0.397498</t>
-  </si>
-  <si>
-    <t>0.416711</t>
-  </si>
-  <si>
-    <t>12.629529</t>
-  </si>
-  <si>
-    <t>119</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>83</t>
-  </si>
-  <si>
-    <t>82</t>
-  </si>
-  <si>
-    <t>AI这么强，为什么大部分公司用不起来？#假期宅家日记 #科技下一站 #我在抖音聊科技 #一本正经说实在话 #ai</t>
-  </si>
-  <si>
-    <t>2026-05-04 11:20:35</t>
-  </si>
-  <si>
-    <t>605</t>
-  </si>
-  <si>
-    <t>0.021595</t>
-  </si>
-  <si>
-    <t>0.401550</t>
-  </si>
-  <si>
-    <t>0.327132</t>
-  </si>
-  <si>
-    <t>27.912722</t>
-  </si>
-  <si>
-    <t>为什么免费AI工具反而更值得警惕？#我在抖音聊科技 #科技下一站 #创业者说真话 #假期宅家日记 #AI</t>
-  </si>
-  <si>
-    <t>2026-05-03 08:43:00</t>
-  </si>
-  <si>
-    <t>2912</t>
-  </si>
-  <si>
-    <t>0.020157</t>
-  </si>
-  <si>
-    <t>0.499656</t>
-  </si>
-  <si>
-    <t>0.267010</t>
-  </si>
-  <si>
-    <t>20.895043</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>普通人用AI做副业 的方法 #科技下一站 #与ai同行 #假期宅家日记#副业 #自动化办公</t>
-  </si>
-  <si>
-    <t>2026-05-02 16:29:45</t>
-  </si>
-  <si>
-    <t>3-5min视频</t>
-  </si>
-  <si>
-    <t>163</t>
-  </si>
-  <si>
-    <t>0.000000</t>
-  </si>
-  <si>
-    <t>0.243902</t>
-  </si>
-  <si>
-    <t>0.107623</t>
-  </si>
-  <si>
-    <t>0.570732</t>
-  </si>
-  <si>
-    <t>8.406699</t>
-  </si>
-  <si>
-    <t>AI这么火，为什么一堆公司倒闭了？#科技下一站 #还有什么是不能ai的 #与ai同行 #大模型 #假期宅家日记</t>
-  </si>
-  <si>
-    <t>2026-04-30 22:40:21</t>
-  </si>
-  <si>
-    <t>3004</t>
-  </si>
-  <si>
-    <t>0.045055</t>
-  </si>
-  <si>
-    <t>0.547213</t>
-  </si>
-  <si>
-    <t>0.281639</t>
-  </si>
-  <si>
-    <t>29.334195</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>AI不会取代你的工作，但会用AI的人会 #AI焦虑 #自动化办公 #科技改变生活 #大模型</t>
-  </si>
-  <si>
-    <t>2026-04-30 22:00:53</t>
-  </si>
-  <si>
-    <t>177</t>
-  </si>
-  <si>
-    <t>0.026882</t>
-  </si>
-  <si>
-    <t>0.230000</t>
-  </si>
-  <si>
-    <t>0.585000</t>
-  </si>
-  <si>
-    <t>23.851485</t>
-  </si>
-  <si>
-    <t>普通人上大学，千万别学ai。 #科技下一站 #还有什么是不能ai的 #与ai同行 #高考 #专业</t>
-  </si>
-  <si>
-    <t>2026-04-29 15:08:15</t>
-  </si>
-  <si>
-    <t>557</t>
-  </si>
-  <si>
-    <t>0.021544</t>
-  </si>
-  <si>
-    <t>0.364780</t>
-  </si>
-  <si>
-    <t>0.378931</t>
-  </si>
-  <si>
-    <t>15.992175</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>家人们，我把AI的价格秘密整理出来了#说真话 #职场干货 #科技下一站 #还有什么是不能ai的 #与ai同行</t>
-  </si>
-  <si>
-    <t>2026-04-29 07:03:00</t>
-  </si>
-  <si>
-    <t>240</t>
-  </si>
-  <si>
-    <t>0.049180</t>
-  </si>
-  <si>
-    <t>0.274809</t>
-  </si>
-  <si>
-    <t>0.519084</t>
-  </si>
-  <si>
-    <t>12.419847</t>
-  </si>
-  <si>
-    <t>明明国内算力更稀缺，为什么反而更便 #科技下一站 #与ai同行 #token</t>
-  </si>
-  <si>
-    <t>2026-04-28 19:57:16</t>
-  </si>
-  <si>
-    <t>11007</t>
-  </si>
-  <si>
-    <t>0.052601</t>
-  </si>
-  <si>
-    <t>0.491792</t>
-  </si>
-  <si>
-    <t>0.293581</t>
-  </si>
-  <si>
-    <t>23.674136</t>
-  </si>
-  <si>
-    <t>164</t>
-  </si>
-  <si>
-    <t>84</t>
-  </si>
-  <si>
-    <t>165</t>
-  </si>
-  <si>
     <t>别人聊 AI 的话题，我连插嘴的资格都没有 #科技下一站 #AI编程 #大模型</t>
   </si>
   <si>
@@ -621,16 +765,16 @@
     <t>238</t>
   </si>
   <si>
-    <t>0.008696</t>
-  </si>
-  <si>
-    <t>0.207171</t>
-  </si>
-  <si>
-    <t>0.565737</t>
-  </si>
-  <si>
-    <t>6.333333</t>
+    <t>0.008658</t>
+  </si>
+  <si>
+    <t>0.206349</t>
+  </si>
+  <si>
+    <t>0.567460</t>
+  </si>
+  <si>
+    <t>6.312253</t>
   </si>
   <si>
     <t>AI编程不是选修课，是打工人的必修课！ #科技下一站 #AI编程 #大模型 #智能体</t>
@@ -639,19 +783,19 @@
     <t>2026-04-22 11:42:56</t>
   </si>
   <si>
-    <t>202</t>
-  </si>
-  <si>
-    <t>0.014778</t>
-  </si>
-  <si>
-    <t>0.270270</t>
-  </si>
-  <si>
-    <t>0.486486</t>
-  </si>
-  <si>
-    <t>15.058559</t>
+    <t>204</t>
+  </si>
+  <si>
+    <t>0.014634</t>
+  </si>
+  <si>
+    <t>0.272321</t>
+  </si>
+  <si>
+    <t>0.482143</t>
+  </si>
+  <si>
+    <t>14.973214</t>
   </si>
   <si>
     <t>好险！差点被裁，多亏我学了AI.给0基础的AI入门课，不用担心听不懂、学不会。#这是个真实的事情 #先定一个小目标 #科技下一站 #与ai同行</t>
@@ -663,16 +807,163 @@
     <t>图文</t>
   </si>
   <si>
-    <t>205</t>
-  </si>
-  <si>
-    <t>0.099476</t>
-  </si>
-  <si>
-    <t>0.486111</t>
-  </si>
-  <si>
-    <t>4.092593</t>
+    <t>212</t>
+  </si>
+  <si>
+    <t>0.098446</t>
+  </si>
+  <si>
+    <t>0.490826</t>
+  </si>
+  <si>
+    <t>4.045455</t>
+  </si>
+  <si>
+    <t>郑州龙虾公开课 #抖音科技风向标 #openclaw #郑州 #人工智能</t>
+  </si>
+  <si>
+    <t>2026-04-10 14:26:12</t>
+  </si>
+  <si>
+    <t>1104</t>
+  </si>
+  <si>
+    <t>0.103025</t>
+  </si>
+  <si>
+    <t>0.298611</t>
+  </si>
+  <si>
+    <t>0.395833</t>
+  </si>
+  <si>
+    <t>5.097710</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>极简三步搭建自己的skills，养龙虾必备 #科技下一站 #超好用的ai指令分享</t>
+  </si>
+  <si>
+    <t>2026-04-01 18:52:54</t>
+  </si>
+  <si>
+    <t>5min+视频</t>
+  </si>
+  <si>
+    <t>5392</t>
+  </si>
+  <si>
+    <t>0.010226</t>
+  </si>
+  <si>
+    <t>0.211640</t>
+  </si>
+  <si>
+    <t>0.550898</t>
+  </si>
+  <si>
+    <t>0.525175</t>
+  </si>
+  <si>
+    <t>15.347664</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>我用龙虾和Coze，自动化提取抖音文案 #科技下一站 #超好用的ai指令分享</t>
+  </si>
+  <si>
+    <t>2026-03-31 22:29:00</t>
+  </si>
+  <si>
+    <t>4207</t>
+  </si>
+  <si>
+    <t>0.011329</t>
+  </si>
+  <si>
+    <t>0.284744</t>
+  </si>
+  <si>
+    <t>0.350230</t>
+  </si>
+  <si>
+    <t>0.431390</t>
+  </si>
+  <si>
+    <t>19.894875</t>
+  </si>
+  <si>
+    <t>WorkBuddy 实操：发票识别自动生成 Excel #workbuddy #openclaw #自动化办公</t>
+  </si>
+  <si>
+    <t>2026-03-26 16:05:44</t>
+  </si>
+  <si>
+    <t>8089</t>
+  </si>
+  <si>
+    <t>0.030402</t>
+  </si>
+  <si>
+    <t>0.545263</t>
+  </si>
+  <si>
+    <t>0.263282</t>
+  </si>
+  <si>
+    <t>37.911007</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>132</t>
+  </si>
+  <si>
+    <t>364</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>保姆级 WorkBuddy 安装教程！腾讯版龙虾 AI 办公 #openclaw #workbuddy #养龙虾</t>
+  </si>
+  <si>
+    <t>2026-03-26 07:30:00</t>
+  </si>
+  <si>
+    <t>5797</t>
+  </si>
+  <si>
+    <t>0.066889</t>
+  </si>
+  <si>
+    <t>0.500765</t>
+  </si>
+  <si>
+    <t>0.722513</t>
+  </si>
+  <si>
+    <t>0.237383</t>
+  </si>
+  <si>
+    <t>28.553941</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>178</t>
+  </si>
+  <si>
+    <t>18</t>
   </si>
 </sst>
 </file>
@@ -1039,7 +1330,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr defaultRowHeight="12.85"/>
   <cols>
     <col collapsed="false" hidden="false" max="1" min="1" style="1" width="9.5"/>
@@ -1168,54 +1459,54 @@
         <v>32</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="L3" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>30</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>18</v>
@@ -1224,187 +1515,187 @@
         <v>19</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>30</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>27</v>
@@ -1412,10 +1703,10 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>18</v>
@@ -1424,98 +1715,98 @@
         <v>19</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>18</v>
@@ -1524,148 +1815,148 @@
         <v>19</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>41</v>
+        <v>103</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="O11" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="P11" s="1" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>124</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="O12" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="J12" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="P12" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>18</v>
@@ -1674,48 +1965,48 @@
         <v>19</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="N13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="P13" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="P13" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>18</v>
@@ -1724,98 +2015,98 @@
         <v>19</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>76</v>
+        <v>29</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>146</v>
+        <v>57</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>148</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J15" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="K15" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="L15" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>18</v>
@@ -1824,48 +2115,48 @@
         <v>19</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>108</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>18</v>
@@ -1874,48 +2165,48 @@
         <v>19</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>108</v>
+        <v>167</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>42</v>
+        <v>168</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>18</v>
@@ -1924,48 +2215,48 @@
         <v>19</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="O18" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O18" s="1" t="s">
-        <v>148</v>
-      </c>
       <c r="P18" s="1" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>18</v>
@@ -1974,48 +2265,48 @@
         <v>19</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="G19" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>185</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>108</v>
+        <v>57</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>18</v>
@@ -2024,66 +2315,66 @@
         <v>19</v>
       </c>
       <c r="E20" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="G20" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>192</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="K20" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="J20" s="1" t="s">
+      <c r="L20" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="N20" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="K20" s="1" t="s">
+      <c r="O20" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="L20" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>197</v>
-      </c>
       <c r="P20" s="1" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="D21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="1" t="s">
+      <c r="F21" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="G21" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="H21" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>203</v>
@@ -2092,19 +2383,19 @@
         <v>204</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="M21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N21" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="N21" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="O21" s="1" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="P21" s="1" t="s">
         <v>27</v>
@@ -2142,33 +2433,33 @@
         <v>211</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>30</v>
+        <v>212</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>214</v>
+        <v>18</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>19</v>
@@ -2180,34 +2471,584 @@
         <v>216</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>153</v>
+        <v>23</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="P26" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="P27" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P28" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P29" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="P30" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="P32" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="P34" s="1" t="s">
+        <v>315</v>
       </c>
     </row>
   </sheetData>
